--- a/data/analysis_pixtral_12b_qwen2_audio/multimodal_event_eval_pixtral_12b_qwen2_audio_w1_0s_h1_0s.xlsx
+++ b/data/analysis_pixtral_12b_qwen2_audio/multimodal_event_eval_pixtral_12b_qwen2_audio_w1_0s_h1_0s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="52">
   <si>
     <t>event</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>sound: engine(0-24), sound: tire_squeal(24-48), sound: impact(48-96), sound: impact(216-240), sound: gunshot_or_explosion(96-120), sound: shout(120-216), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
   </si>
   <si>
     <t>sound: engine(0-24), sound: horn(24-48), sound: shout(48-72), sound: shout(120-168), sound: impact(72-120), sound: impact(168-240), visual: enter_or_exit_vehicle(120-216), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-216), visual: suspicious_near_vehicle(168-240), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-240), visual: vehicle_collision(192-240)</t>
@@ -666,22 +669,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -990,7 +993,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1049,15 +1052,32 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1102,7 +1122,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1119,7 +1139,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1157,13 +1177,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1207,7 +1227,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1251,7 +1271,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1268,7 +1288,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1312,7 +1332,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1400,7 +1420,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1444,7 +1464,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1488,7 +1508,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1552,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1549,7 +1569,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1593,7 +1613,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1637,7 +1657,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1654,7 +1674,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1698,7 +1718,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1715,7 +1735,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1759,7 +1779,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1803,7 +1823,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1847,7 +1867,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1935,7 +1955,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1979,7 +1999,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
